--- a/data/processed/harmonization/Nitrogen__Nitrate_nitrogen/harmonized.xlsx
+++ b/data/processed/harmonization/Nitrogen__Nitrate_nitrogen/harmonized.xlsx
@@ -4054,12 +4054,12 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr"/>
@@ -4102,12 +4102,12 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4:4</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr"/>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5:5</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr"/>
@@ -4198,12 +4198,12 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1:6</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr"/>
@@ -4246,12 +4246,12 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4:9</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr"/>
@@ -4294,12 +4294,12 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6:11</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr"/>
@@ -4342,12 +4342,12 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8:12</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr"/>
@@ -4390,12 +4390,12 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr"/>
@@ -4438,12 +4438,12 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr"/>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>22:15</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Lab ID</t>
+          <t>Core no for CN:Lab ID</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr"/>
@@ -7494,12 +7494,12 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>D11:1:2021</t>
+          <t>D11:2021:1</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr"/>
@@ -7542,12 +7542,12 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>D11:2:2021</t>
+          <t>D11:2021:2</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr"/>
@@ -7590,12 +7590,12 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>D11:3:2021</t>
+          <t>D11:2021:3</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr"/>
@@ -7638,12 +7638,12 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>D12:4:2021</t>
+          <t>D12:2021:4</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr"/>
@@ -7686,12 +7686,12 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>D12:5:2021</t>
+          <t>D12:2021:5</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr"/>
@@ -7734,12 +7734,12 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>D12:6:2021</t>
+          <t>D12:2021:6</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr"/>
@@ -7782,12 +7782,12 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>D13:7:2021</t>
+          <t>D13:2021:7</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr"/>
@@ -7830,12 +7830,12 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>D13:8:2021</t>
+          <t>D13:2021:8</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr"/>
@@ -7878,12 +7878,12 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>D13:9:2021</t>
+          <t>D13:2021:9</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr"/>
@@ -7926,12 +7926,12 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>D14:10:2021</t>
+          <t>D14:2021:10</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr"/>
@@ -7974,12 +7974,12 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>D14:11:2021</t>
+          <t>D14:2021:11</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr"/>
@@ -8022,12 +8022,12 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>D14:12:2021</t>
+          <t>D14:2021:12</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr"/>
@@ -8070,12 +8070,12 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>D15:13:2021</t>
+          <t>D15:2021:13</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr"/>
@@ -8118,12 +8118,12 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>D15:14:2021</t>
+          <t>D15:2021:14</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr"/>
@@ -8166,12 +8166,12 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>D15:15:2021</t>
+          <t>D15:2021:15</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr"/>
@@ -8214,12 +8214,12 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>D16:16:2021</t>
+          <t>D16:2021:16</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr"/>
@@ -8262,12 +8262,12 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>D16:17:2021</t>
+          <t>D16:2021:17</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr"/>
@@ -8310,12 +8310,12 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>D16:18:2021</t>
+          <t>D16:2021:18</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr"/>
@@ -8358,12 +8358,12 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>E1:19:2021</t>
+          <t>E1:2021:19</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr"/>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>E1:20:2021</t>
+          <t>E1:2021:20</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr"/>
@@ -8454,12 +8454,12 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>E1:21:2021</t>
+          <t>E1:2021:21</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr"/>
@@ -8502,12 +8502,12 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>E2:22:2021</t>
+          <t>E2:2021:22</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr"/>
@@ -8550,12 +8550,12 @@
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>E2:23:2021</t>
+          <t>E2:2021:23</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr"/>
@@ -8598,12 +8598,12 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>E2:24:2021</t>
+          <t>E2:2021:24</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr"/>
@@ -8646,12 +8646,12 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>E3:25:2021</t>
+          <t>E3:2021:25</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr"/>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>E3:26:2021</t>
+          <t>E3:2021:26</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr"/>
@@ -8742,12 +8742,12 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>E3:27:2021</t>
+          <t>E3:2021:27</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr"/>
@@ -8790,12 +8790,12 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>E4:28:2021</t>
+          <t>E4:2021:28</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr"/>
@@ -8838,12 +8838,12 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>E4:29:2021</t>
+          <t>E4:2021:29</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr"/>
@@ -8886,12 +8886,12 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>E4:30:2021</t>
+          <t>E4:2021:30</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr"/>
@@ -8934,12 +8934,12 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>E5:31:2021</t>
+          <t>E5:2021:31</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr"/>
@@ -8982,12 +8982,12 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>E5:32:2021</t>
+          <t>E5:2021:32</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr"/>
@@ -9030,12 +9030,12 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>E5:33:2021</t>
+          <t>E5:2021:33</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr"/>
@@ -9078,12 +9078,12 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>E6:34:2021</t>
+          <t>E6:2021:34</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr"/>
@@ -9126,12 +9126,12 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>E6:35:2021</t>
+          <t>E6:2021:35</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr"/>
@@ -9174,12 +9174,12 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>E6:36:2021</t>
+          <t>E6:2021:36</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr"/>
@@ -9222,12 +9222,12 @@
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>D1:38:2021</t>
+          <t>D1:2021:38</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr"/>
@@ -9270,12 +9270,12 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>D1:39:2021</t>
+          <t>D1:2021:39</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr"/>
@@ -9318,12 +9318,12 @@
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>D2:40:2021</t>
+          <t>D2:2021:40</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr"/>
@@ -9366,12 +9366,12 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>D2:41:2021</t>
+          <t>D2:2021:41</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr"/>
@@ -9414,12 +9414,12 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>D2:42:2021</t>
+          <t>D2:2021:42</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr"/>
@@ -9462,12 +9462,12 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>D3:43:2021</t>
+          <t>D3:2021:43</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr"/>
@@ -9510,12 +9510,12 @@
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>D3:44:2021</t>
+          <t>D3:2021:44</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr"/>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>D3:45:2021</t>
+          <t>D3:2021:45</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr"/>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>D4:46:2021</t>
+          <t>D4:2021:46</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr"/>
@@ -9654,12 +9654,12 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>D4:47:2021</t>
+          <t>D4:2021:47</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr"/>
@@ -9702,12 +9702,12 @@
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>D4:48:2021</t>
+          <t>D4:2021:48</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr"/>
@@ -9750,12 +9750,12 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>D5:49:2021</t>
+          <t>D5:2021:49</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr"/>
@@ -9798,12 +9798,12 @@
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>D5:50:2021</t>
+          <t>D5:2021:50</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr"/>
@@ -9846,12 +9846,12 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>D5:51:2021</t>
+          <t>D5:2021:51</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr"/>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>D6:52:2021</t>
+          <t>D6:2021:52</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr"/>
@@ -9942,12 +9942,12 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>D6:53:2021</t>
+          <t>D6:2021:53</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr"/>
@@ -9990,12 +9990,12 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>D6:54:2021</t>
+          <t>D6:2021:54</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr"/>
@@ -10038,12 +10038,12 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>E7:55:2021</t>
+          <t>E7:2021:55</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr"/>
@@ -10086,12 +10086,12 @@
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>E7:56:2021</t>
+          <t>E7:2021:56</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr"/>
@@ -10134,12 +10134,12 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>E7:57:2021</t>
+          <t>E7:2021:57</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr"/>
@@ -10182,12 +10182,12 @@
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>E8:58:2021</t>
+          <t>E8:2021:58</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr"/>
@@ -10230,12 +10230,12 @@
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>E8:59:2021</t>
+          <t>E8:2021:59</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr"/>
@@ -10278,12 +10278,12 @@
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>E8:60:2021</t>
+          <t>E8:2021:60</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr"/>
@@ -10326,12 +10326,12 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>E9:61:2021</t>
+          <t>E9:2021:61</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr"/>
@@ -10374,12 +10374,12 @@
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>E9:62:2021</t>
+          <t>E9:2021:62</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr"/>
@@ -10422,12 +10422,12 @@
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>E9:63:2021</t>
+          <t>E9:2021:63</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr"/>
@@ -10470,12 +10470,12 @@
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>E10:64:2021</t>
+          <t>E10:2021:64</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr"/>
@@ -10518,12 +10518,12 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>E10:65:2021</t>
+          <t>E10:2021:65</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr"/>
@@ -10566,12 +10566,12 @@
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>E10:66:2021</t>
+          <t>E10:2021:66</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr"/>
@@ -10614,12 +10614,12 @@
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>E11:67:2021</t>
+          <t>E11:2021:67</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr"/>
@@ -10662,12 +10662,12 @@
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>E11:68:2021</t>
+          <t>E11:2021:68</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr"/>
@@ -10710,12 +10710,12 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>E11:69:2021</t>
+          <t>E11:2021:69</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr"/>
@@ -10758,12 +10758,12 @@
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>E12:70:2021</t>
+          <t>E12:2021:70</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr"/>
@@ -10806,12 +10806,12 @@
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>E12:71:2021</t>
+          <t>E12:2021:71</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr"/>
@@ -10854,12 +10854,12 @@
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>E12:72:2021</t>
+          <t>E12:2021:72</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr"/>
@@ -10902,12 +10902,12 @@
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>D11:1:2022</t>
+          <t>D11:2022:1</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr"/>
@@ -10950,12 +10950,12 @@
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>D11:2:2022</t>
+          <t>D11:2022:2</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr"/>
@@ -10998,12 +10998,12 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>D11:3:2022</t>
+          <t>D11:2022:3</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr"/>
@@ -11046,12 +11046,12 @@
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>D12:4:2022</t>
+          <t>D12:2022:4</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr"/>
@@ -11094,12 +11094,12 @@
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>D12:5:2022</t>
+          <t>D12:2022:5</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr"/>
@@ -11142,12 +11142,12 @@
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>D12:6:2022</t>
+          <t>D12:2022:6</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr"/>
@@ -11190,12 +11190,12 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>D13:7:2022</t>
+          <t>D13:2022:7</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr"/>
@@ -11238,12 +11238,12 @@
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>D13:8:2022</t>
+          <t>D13:2022:8</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr"/>
@@ -11286,12 +11286,12 @@
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>D13:9:2022</t>
+          <t>D13:2022:9</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr"/>
@@ -11334,12 +11334,12 @@
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>D14:10:2022</t>
+          <t>D14:2022:10</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr"/>
@@ -11382,12 +11382,12 @@
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>D14:11:2022</t>
+          <t>D14:2022:11</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr"/>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>D14:12:2022</t>
+          <t>D14:2022:12</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr"/>
@@ -11478,12 +11478,12 @@
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>D15:13:2022</t>
+          <t>D15:2022:13</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr"/>
@@ -11526,12 +11526,12 @@
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>D15:14:2022</t>
+          <t>D15:2022:14</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr"/>
@@ -11574,12 +11574,12 @@
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>D15:15:2022</t>
+          <t>D15:2022:15</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr"/>
@@ -11622,12 +11622,12 @@
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>D16:16:2022</t>
+          <t>D16:2022:16</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr"/>
@@ -11670,12 +11670,12 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>D16:17:2022</t>
+          <t>D16:2022:17</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr"/>
@@ -11718,12 +11718,12 @@
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>D16:18:2022</t>
+          <t>D16:2022:18</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr"/>
@@ -11766,12 +11766,12 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>E1:19:2022</t>
+          <t>E1:2022:19</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr"/>
@@ -11814,12 +11814,12 @@
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>E1:20:2022</t>
+          <t>E1:2022:20</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr"/>
@@ -11862,12 +11862,12 @@
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>E1:21:2022</t>
+          <t>E1:2022:21</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr"/>
@@ -11910,12 +11910,12 @@
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>E2:22:2022</t>
+          <t>E2:2022:22</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr"/>
@@ -11958,12 +11958,12 @@
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>E2:23:2022</t>
+          <t>E2:2022:23</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr"/>
@@ -12006,12 +12006,12 @@
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>E2:24:2022</t>
+          <t>E2:2022:24</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr"/>
@@ -12054,12 +12054,12 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>E3:25:2022</t>
+          <t>E3:2022:25</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr"/>
@@ -12102,12 +12102,12 @@
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>E3:26:2022</t>
+          <t>E3:2022:26</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr"/>
@@ -12150,12 +12150,12 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>E3:27:2022</t>
+          <t>E3:2022:27</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr"/>
@@ -12198,12 +12198,12 @@
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>E4:28:2022</t>
+          <t>E4:2022:28</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr"/>
@@ -12246,12 +12246,12 @@
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>E4:29:2022</t>
+          <t>E4:2022:29</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr"/>
@@ -12294,12 +12294,12 @@
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>E4:30:2022</t>
+          <t>E4:2022:30</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr"/>
@@ -12342,12 +12342,12 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>E5:31:2022</t>
+          <t>E5:2022:31</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr"/>
@@ -12390,12 +12390,12 @@
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>E5:32:2022</t>
+          <t>E5:2022:32</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr"/>
@@ -12438,12 +12438,12 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>E5:33:2022</t>
+          <t>E5:2022:33</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr"/>
@@ -12486,12 +12486,12 @@
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>E6:34:2022</t>
+          <t>E6:2022:34</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr"/>
@@ -12534,12 +12534,12 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>E6:35:2022</t>
+          <t>E6:2022:35</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr"/>
@@ -12582,12 +12582,12 @@
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>E6:36:2022</t>
+          <t>E6:2022:36</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr"/>
@@ -12630,12 +12630,12 @@
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>D1:37:2022</t>
+          <t>D1:2022:37</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr"/>
@@ -12678,12 +12678,12 @@
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>D1:38:2022</t>
+          <t>D1:2022:38</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr"/>
@@ -12726,12 +12726,12 @@
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>D1:39:2022</t>
+          <t>D1:2022:39</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr"/>
@@ -12774,12 +12774,12 @@
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>D2:40:2022</t>
+          <t>D2:2022:40</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr"/>
@@ -12822,12 +12822,12 @@
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>D2:41:2022</t>
+          <t>D2:2022:41</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr"/>
@@ -12870,12 +12870,12 @@
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>D2:42:2022</t>
+          <t>D2:2022:42</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr"/>
@@ -12918,12 +12918,12 @@
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>D3:43:2022</t>
+          <t>D3:2022:43</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr"/>
@@ -12966,12 +12966,12 @@
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>D3:44:2022</t>
+          <t>D3:2022:44</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E255" s="2" t="inlineStr"/>
@@ -13014,12 +13014,12 @@
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>D3:45:2022</t>
+          <t>D3:2022:45</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr"/>
@@ -13062,12 +13062,12 @@
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>D4:46:2022</t>
+          <t>D4:2022:46</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr"/>
@@ -13110,12 +13110,12 @@
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>D4:47:2022</t>
+          <t>D4:2022:47</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr"/>
@@ -13158,12 +13158,12 @@
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>D4:48:2022</t>
+          <t>D4:2022:48</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr"/>
@@ -13206,12 +13206,12 @@
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>D5:49:2022</t>
+          <t>D5:2022:49</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr"/>
@@ -13254,12 +13254,12 @@
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>D5:50:2022</t>
+          <t>D5:2022:50</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr"/>
@@ -13302,12 +13302,12 @@
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>D5:51:2022</t>
+          <t>D5:2022:51</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr"/>
@@ -13350,12 +13350,12 @@
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>D6:52:2022</t>
+          <t>D6:2022:52</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr"/>
@@ -13398,12 +13398,12 @@
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>D6:53:2022</t>
+          <t>D6:2022:53</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr"/>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>D6:54:2022</t>
+          <t>D6:2022:54</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr"/>
@@ -13494,12 +13494,12 @@
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>E7:55:2022</t>
+          <t>E7:2022:55</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr"/>
@@ -13542,12 +13542,12 @@
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>E7:56:2022</t>
+          <t>E7:2022:56</t>
         </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E267" s="2" t="inlineStr"/>
@@ -13590,12 +13590,12 @@
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>E7:57:2022</t>
+          <t>E7:2022:57</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr"/>
@@ -13638,12 +13638,12 @@
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>E8:58:2022</t>
+          <t>E8:2022:58</t>
         </is>
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr"/>
@@ -13686,12 +13686,12 @@
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>E8:59:2022</t>
+          <t>E8:2022:59</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr"/>
@@ -13734,12 +13734,12 @@
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>E8:60:2022</t>
+          <t>E8:2022:60</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr"/>
@@ -13782,12 +13782,12 @@
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>E9:61:2022</t>
+          <t>E9:2022:61</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr"/>
@@ -13830,12 +13830,12 @@
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>E9:62:2022</t>
+          <t>E9:2022:62</t>
         </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E273" s="2" t="inlineStr"/>
@@ -13878,12 +13878,12 @@
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>E9:63:2022</t>
+          <t>E9:2022:63</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr"/>
@@ -13926,12 +13926,12 @@
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>E10:64:2022</t>
+          <t>E10:2022:64</t>
         </is>
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr"/>
@@ -13974,12 +13974,12 @@
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>E10:65:2022</t>
+          <t>E10:2022:65</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr"/>
@@ -14022,12 +14022,12 @@
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>E10:66:2022</t>
+          <t>E10:2022:66</t>
         </is>
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr"/>
@@ -14070,12 +14070,12 @@
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>E11:69:2022</t>
+          <t>E11:2022:69</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr"/>
@@ -14118,12 +14118,12 @@
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>E12:70:2022</t>
+          <t>E12:2022:70</t>
         </is>
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr"/>
@@ -14166,12 +14166,12 @@
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>E12:71:2022</t>
+          <t>E12:2022:71</t>
         </is>
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr"/>
@@ -14214,12 +14214,12 @@
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>E12:72:2022</t>
+          <t>E12:2022:72</t>
         </is>
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr"/>
@@ -14262,12 +14262,12 @@
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>D11:1:2021</t>
+          <t>D11:2021:1</t>
         </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr"/>
@@ -14310,12 +14310,12 @@
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>D11:2:2021</t>
+          <t>D11:2021:2</t>
         </is>
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr"/>
@@ -14358,12 +14358,12 @@
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>D11:3:2021</t>
+          <t>D11:2021:3</t>
         </is>
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E284" s="2" t="inlineStr"/>
@@ -14406,12 +14406,12 @@
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>D12:4:2021</t>
+          <t>D12:2021:4</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr"/>
@@ -14454,12 +14454,12 @@
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>D12:5:2021</t>
+          <t>D12:2021:5</t>
         </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr"/>
@@ -14502,12 +14502,12 @@
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>D12:6:2021</t>
+          <t>D12:2021:6</t>
         </is>
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr"/>
@@ -14550,12 +14550,12 @@
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>D13:7:2021</t>
+          <t>D13:2021:7</t>
         </is>
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr"/>
@@ -14598,12 +14598,12 @@
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>D13:8:2021</t>
+          <t>D13:2021:8</t>
         </is>
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E289" s="2" t="inlineStr"/>
@@ -14646,12 +14646,12 @@
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>D13:9:2021</t>
+          <t>D13:2021:9</t>
         </is>
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E290" s="2" t="inlineStr"/>
@@ -14694,12 +14694,12 @@
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>D14:10:2021</t>
+          <t>D14:2021:10</t>
         </is>
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E291" s="2" t="inlineStr"/>
@@ -14742,12 +14742,12 @@
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>D14:11:2021</t>
+          <t>D14:2021:11</t>
         </is>
       </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E292" s="2" t="inlineStr"/>
@@ -14790,12 +14790,12 @@
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>D14:12:2021</t>
+          <t>D14:2021:12</t>
         </is>
       </c>
       <c r="D293" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E293" s="2" t="inlineStr"/>
@@ -14838,12 +14838,12 @@
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>D15:13:2021</t>
+          <t>D15:2021:13</t>
         </is>
       </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E294" s="2" t="inlineStr"/>
@@ -14886,12 +14886,12 @@
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>D15:14:2021</t>
+          <t>D15:2021:14</t>
         </is>
       </c>
       <c r="D295" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E295" s="2" t="inlineStr"/>
@@ -14934,12 +14934,12 @@
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>D15:15:2021</t>
+          <t>D15:2021:15</t>
         </is>
       </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr"/>
@@ -14982,12 +14982,12 @@
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>D16:16:2021</t>
+          <t>D16:2021:16</t>
         </is>
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E297" s="2" t="inlineStr"/>
@@ -15030,12 +15030,12 @@
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>D16:17:2021</t>
+          <t>D16:2021:17</t>
         </is>
       </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr"/>
@@ -15078,12 +15078,12 @@
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>D16:18:2021</t>
+          <t>D16:2021:18</t>
         </is>
       </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E299" s="2" t="inlineStr"/>
@@ -15126,12 +15126,12 @@
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>E1:19:2021</t>
+          <t>E1:2021:19</t>
         </is>
       </c>
       <c r="D300" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E300" s="2" t="inlineStr"/>
@@ -15174,12 +15174,12 @@
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>E1:20:2021</t>
+          <t>E1:2021:20</t>
         </is>
       </c>
       <c r="D301" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E301" s="2" t="inlineStr"/>
@@ -15222,12 +15222,12 @@
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>E1:21:2021</t>
+          <t>E1:2021:21</t>
         </is>
       </c>
       <c r="D302" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E302" s="2" t="inlineStr"/>
@@ -15270,12 +15270,12 @@
       </c>
       <c r="C303" s="2" t="inlineStr">
         <is>
-          <t>E2:22:2021</t>
+          <t>E2:2021:22</t>
         </is>
       </c>
       <c r="D303" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E303" s="2" t="inlineStr"/>
@@ -15318,12 +15318,12 @@
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>E2:23:2021</t>
+          <t>E2:2021:23</t>
         </is>
       </c>
       <c r="D304" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E304" s="2" t="inlineStr"/>
@@ -15366,12 +15366,12 @@
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>E2:24:2021</t>
+          <t>E2:2021:24</t>
         </is>
       </c>
       <c r="D305" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E305" s="2" t="inlineStr"/>
@@ -15414,12 +15414,12 @@
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>E3:25:2021</t>
+          <t>E3:2021:25</t>
         </is>
       </c>
       <c r="D306" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E306" s="2" t="inlineStr"/>
@@ -15462,12 +15462,12 @@
       </c>
       <c r="C307" s="2" t="inlineStr">
         <is>
-          <t>E3:26:2021</t>
+          <t>E3:2021:26</t>
         </is>
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E307" s="2" t="inlineStr"/>
@@ -15510,12 +15510,12 @@
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>E3:27:2021</t>
+          <t>E3:2021:27</t>
         </is>
       </c>
       <c r="D308" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E308" s="2" t="inlineStr"/>
@@ -15558,12 +15558,12 @@
       </c>
       <c r="C309" s="2" t="inlineStr">
         <is>
-          <t>E4:28:2021</t>
+          <t>E4:2021:28</t>
         </is>
       </c>
       <c r="D309" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E309" s="2" t="inlineStr"/>
@@ -15606,12 +15606,12 @@
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>E4:29:2021</t>
+          <t>E4:2021:29</t>
         </is>
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E310" s="2" t="inlineStr"/>
@@ -15654,12 +15654,12 @@
       </c>
       <c r="C311" s="2" t="inlineStr">
         <is>
-          <t>E4:30:2021</t>
+          <t>E4:2021:30</t>
         </is>
       </c>
       <c r="D311" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E311" s="2" t="inlineStr"/>
@@ -15702,12 +15702,12 @@
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>E5:31:2021</t>
+          <t>E5:2021:31</t>
         </is>
       </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E312" s="2" t="inlineStr"/>
@@ -15750,12 +15750,12 @@
       </c>
       <c r="C313" s="2" t="inlineStr">
         <is>
-          <t>E5:32:2021</t>
+          <t>E5:2021:32</t>
         </is>
       </c>
       <c r="D313" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E313" s="2" t="inlineStr"/>
@@ -15798,12 +15798,12 @@
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>E5:33:2021</t>
+          <t>E5:2021:33</t>
         </is>
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E314" s="2" t="inlineStr"/>
@@ -15846,12 +15846,12 @@
       </c>
       <c r="C315" s="2" t="inlineStr">
         <is>
-          <t>E6:34:2021</t>
+          <t>E6:2021:34</t>
         </is>
       </c>
       <c r="D315" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E315" s="2" t="inlineStr"/>
@@ -15894,12 +15894,12 @@
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>E6:35:2021</t>
+          <t>E6:2021:35</t>
         </is>
       </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E316" s="2" t="inlineStr"/>
@@ -15942,12 +15942,12 @@
       </c>
       <c r="C317" s="2" t="inlineStr">
         <is>
-          <t>E6:36:2021</t>
+          <t>E6:2021:36</t>
         </is>
       </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E317" s="2" t="inlineStr"/>
@@ -15990,12 +15990,12 @@
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>D1:38:2021</t>
+          <t>D1:2021:38</t>
         </is>
       </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E318" s="2" t="inlineStr"/>
@@ -16038,12 +16038,12 @@
       </c>
       <c r="C319" s="2" t="inlineStr">
         <is>
-          <t>D1:39:2021</t>
+          <t>D1:2021:39</t>
         </is>
       </c>
       <c r="D319" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E319" s="2" t="inlineStr"/>
@@ -16086,12 +16086,12 @@
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>D2:40:2021</t>
+          <t>D2:2021:40</t>
         </is>
       </c>
       <c r="D320" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E320" s="2" t="inlineStr"/>
@@ -16134,12 +16134,12 @@
       </c>
       <c r="C321" s="2" t="inlineStr">
         <is>
-          <t>D2:41:2021</t>
+          <t>D2:2021:41</t>
         </is>
       </c>
       <c r="D321" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E321" s="2" t="inlineStr"/>
@@ -16182,12 +16182,12 @@
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>D2:42:2021</t>
+          <t>D2:2021:42</t>
         </is>
       </c>
       <c r="D322" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E322" s="2" t="inlineStr"/>
@@ -16230,12 +16230,12 @@
       </c>
       <c r="C323" s="2" t="inlineStr">
         <is>
-          <t>D3:43:2021</t>
+          <t>D3:2021:43</t>
         </is>
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E323" s="2" t="inlineStr"/>
@@ -16278,12 +16278,12 @@
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>D3:44:2021</t>
+          <t>D3:2021:44</t>
         </is>
       </c>
       <c r="D324" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E324" s="2" t="inlineStr"/>
@@ -16326,12 +16326,12 @@
       </c>
       <c r="C325" s="2" t="inlineStr">
         <is>
-          <t>D3:45:2021</t>
+          <t>D3:2021:45</t>
         </is>
       </c>
       <c r="D325" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E325" s="2" t="inlineStr"/>
@@ -16374,12 +16374,12 @@
       </c>
       <c r="C326" s="2" t="inlineStr">
         <is>
-          <t>D4:46:2021</t>
+          <t>D4:2021:46</t>
         </is>
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E326" s="2" t="inlineStr"/>
@@ -16422,12 +16422,12 @@
       </c>
       <c r="C327" s="2" t="inlineStr">
         <is>
-          <t>D4:47:2021</t>
+          <t>D4:2021:47</t>
         </is>
       </c>
       <c r="D327" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E327" s="2" t="inlineStr"/>
@@ -16470,12 +16470,12 @@
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>D4:48:2021</t>
+          <t>D4:2021:48</t>
         </is>
       </c>
       <c r="D328" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E328" s="2" t="inlineStr"/>
@@ -16518,12 +16518,12 @@
       </c>
       <c r="C329" s="2" t="inlineStr">
         <is>
-          <t>D5:49:2021</t>
+          <t>D5:2021:49</t>
         </is>
       </c>
       <c r="D329" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E329" s="2" t="inlineStr"/>
@@ -16566,12 +16566,12 @@
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>D5:50:2021</t>
+          <t>D5:2021:50</t>
         </is>
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E330" s="2" t="inlineStr"/>
@@ -16614,12 +16614,12 @@
       </c>
       <c r="C331" s="2" t="inlineStr">
         <is>
-          <t>D5:51:2021</t>
+          <t>D5:2021:51</t>
         </is>
       </c>
       <c r="D331" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E331" s="2" t="inlineStr"/>
@@ -16662,12 +16662,12 @@
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>D6:52:2021</t>
+          <t>D6:2021:52</t>
         </is>
       </c>
       <c r="D332" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E332" s="2" t="inlineStr"/>
@@ -16710,12 +16710,12 @@
       </c>
       <c r="C333" s="2" t="inlineStr">
         <is>
-          <t>D6:53:2021</t>
+          <t>D6:2021:53</t>
         </is>
       </c>
       <c r="D333" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E333" s="2" t="inlineStr"/>
@@ -16758,12 +16758,12 @@
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>D6:54:2021</t>
+          <t>D6:2021:54</t>
         </is>
       </c>
       <c r="D334" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E334" s="2" t="inlineStr"/>
@@ -16806,12 +16806,12 @@
       </c>
       <c r="C335" s="2" t="inlineStr">
         <is>
-          <t>E7:55:2021</t>
+          <t>E7:2021:55</t>
         </is>
       </c>
       <c r="D335" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E335" s="2" t="inlineStr"/>
@@ -16854,12 +16854,12 @@
       </c>
       <c r="C336" s="2" t="inlineStr">
         <is>
-          <t>E7:56:2021</t>
+          <t>E7:2021:56</t>
         </is>
       </c>
       <c r="D336" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E336" s="2" t="inlineStr"/>
@@ -16902,12 +16902,12 @@
       </c>
       <c r="C337" s="2" t="inlineStr">
         <is>
-          <t>E7:57:2021</t>
+          <t>E7:2021:57</t>
         </is>
       </c>
       <c r="D337" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E337" s="2" t="inlineStr"/>
@@ -16950,12 +16950,12 @@
       </c>
       <c r="C338" s="2" t="inlineStr">
         <is>
-          <t>E8:58:2021</t>
+          <t>E8:2021:58</t>
         </is>
       </c>
       <c r="D338" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E338" s="2" t="inlineStr"/>
@@ -16998,12 +16998,12 @@
       </c>
       <c r="C339" s="2" t="inlineStr">
         <is>
-          <t>E8:59:2021</t>
+          <t>E8:2021:59</t>
         </is>
       </c>
       <c r="D339" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E339" s="2" t="inlineStr"/>
@@ -17046,12 +17046,12 @@
       </c>
       <c r="C340" s="2" t="inlineStr">
         <is>
-          <t>E8:60:2021</t>
+          <t>E8:2021:60</t>
         </is>
       </c>
       <c r="D340" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E340" s="2" t="inlineStr"/>
@@ -17094,12 +17094,12 @@
       </c>
       <c r="C341" s="2" t="inlineStr">
         <is>
-          <t>E9:61:2021</t>
+          <t>E9:2021:61</t>
         </is>
       </c>
       <c r="D341" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E341" s="2" t="inlineStr"/>
@@ -17142,12 +17142,12 @@
       </c>
       <c r="C342" s="2" t="inlineStr">
         <is>
-          <t>E9:62:2021</t>
+          <t>E9:2021:62</t>
         </is>
       </c>
       <c r="D342" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E342" s="2" t="inlineStr"/>
@@ -17190,12 +17190,12 @@
       </c>
       <c r="C343" s="2" t="inlineStr">
         <is>
-          <t>E9:63:2021</t>
+          <t>E9:2021:63</t>
         </is>
       </c>
       <c r="D343" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E343" s="2" t="inlineStr"/>
@@ -17238,12 +17238,12 @@
       </c>
       <c r="C344" s="2" t="inlineStr">
         <is>
-          <t>E10:64:2021</t>
+          <t>E10:2021:64</t>
         </is>
       </c>
       <c r="D344" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E344" s="2" t="inlineStr"/>
@@ -17286,12 +17286,12 @@
       </c>
       <c r="C345" s="2" t="inlineStr">
         <is>
-          <t>E10:65:2021</t>
+          <t>E10:2021:65</t>
         </is>
       </c>
       <c r="D345" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E345" s="2" t="inlineStr"/>
@@ -17334,12 +17334,12 @@
       </c>
       <c r="C346" s="2" t="inlineStr">
         <is>
-          <t>E10:66:2021</t>
+          <t>E10:2021:66</t>
         </is>
       </c>
       <c r="D346" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E346" s="2" t="inlineStr"/>
@@ -17382,12 +17382,12 @@
       </c>
       <c r="C347" s="2" t="inlineStr">
         <is>
-          <t>E11:67:2021</t>
+          <t>E11:2021:67</t>
         </is>
       </c>
       <c r="D347" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E347" s="2" t="inlineStr"/>
@@ -17430,12 +17430,12 @@
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>E11:68:2021</t>
+          <t>E11:2021:68</t>
         </is>
       </c>
       <c r="D348" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E348" s="2" t="inlineStr"/>
@@ -17478,12 +17478,12 @@
       </c>
       <c r="C349" s="2" t="inlineStr">
         <is>
-          <t>E11:69:2021</t>
+          <t>E11:2021:69</t>
         </is>
       </c>
       <c r="D349" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E349" s="2" t="inlineStr"/>
@@ -17526,12 +17526,12 @@
       </c>
       <c r="C350" s="2" t="inlineStr">
         <is>
-          <t>E12:70:2021</t>
+          <t>E12:2021:70</t>
         </is>
       </c>
       <c r="D350" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E350" s="2" t="inlineStr"/>
@@ -17574,12 +17574,12 @@
       </c>
       <c r="C351" s="2" t="inlineStr">
         <is>
-          <t>E12:71:2021</t>
+          <t>E12:2021:71</t>
         </is>
       </c>
       <c r="D351" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E351" s="2" t="inlineStr"/>
@@ -17622,12 +17622,12 @@
       </c>
       <c r="C352" s="2" t="inlineStr">
         <is>
-          <t>E12:72:2021</t>
+          <t>E12:2021:72</t>
         </is>
       </c>
       <c r="D352" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E352" s="2" t="inlineStr"/>
@@ -17670,12 +17670,12 @@
       </c>
       <c r="C353" s="2" t="inlineStr">
         <is>
-          <t>D11:1:2022</t>
+          <t>D11:2022:1</t>
         </is>
       </c>
       <c r="D353" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E353" s="2" t="inlineStr"/>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="C354" s="2" t="inlineStr">
         <is>
-          <t>D11:2:2022</t>
+          <t>D11:2022:2</t>
         </is>
       </c>
       <c r="D354" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E354" s="2" t="inlineStr"/>
@@ -17766,12 +17766,12 @@
       </c>
       <c r="C355" s="2" t="inlineStr">
         <is>
-          <t>D11:3:2022</t>
+          <t>D11:2022:3</t>
         </is>
       </c>
       <c r="D355" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E355" s="2" t="inlineStr"/>
@@ -17814,12 +17814,12 @@
       </c>
       <c r="C356" s="2" t="inlineStr">
         <is>
-          <t>D12:4:2022</t>
+          <t>D12:2022:4</t>
         </is>
       </c>
       <c r="D356" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E356" s="2" t="inlineStr"/>
@@ -17862,12 +17862,12 @@
       </c>
       <c r="C357" s="2" t="inlineStr">
         <is>
-          <t>D12:5:2022</t>
+          <t>D12:2022:5</t>
         </is>
       </c>
       <c r="D357" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E357" s="2" t="inlineStr"/>
@@ -17910,12 +17910,12 @@
       </c>
       <c r="C358" s="2" t="inlineStr">
         <is>
-          <t>D12:6:2022</t>
+          <t>D12:2022:6</t>
         </is>
       </c>
       <c r="D358" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E358" s="2" t="inlineStr"/>
@@ -17958,12 +17958,12 @@
       </c>
       <c r="C359" s="2" t="inlineStr">
         <is>
-          <t>D13:7:2022</t>
+          <t>D13:2022:7</t>
         </is>
       </c>
       <c r="D359" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E359" s="2" t="inlineStr"/>
@@ -18006,12 +18006,12 @@
       </c>
       <c r="C360" s="2" t="inlineStr">
         <is>
-          <t>D13:8:2022</t>
+          <t>D13:2022:8</t>
         </is>
       </c>
       <c r="D360" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E360" s="2" t="inlineStr"/>
@@ -18054,12 +18054,12 @@
       </c>
       <c r="C361" s="2" t="inlineStr">
         <is>
-          <t>D13:9:2022</t>
+          <t>D13:2022:9</t>
         </is>
       </c>
       <c r="D361" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E361" s="2" t="inlineStr"/>
@@ -18102,12 +18102,12 @@
       </c>
       <c r="C362" s="2" t="inlineStr">
         <is>
-          <t>D14:10:2022</t>
+          <t>D14:2022:10</t>
         </is>
       </c>
       <c r="D362" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E362" s="2" t="inlineStr"/>
@@ -18150,12 +18150,12 @@
       </c>
       <c r="C363" s="2" t="inlineStr">
         <is>
-          <t>D14:11:2022</t>
+          <t>D14:2022:11</t>
         </is>
       </c>
       <c r="D363" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E363" s="2" t="inlineStr"/>
@@ -18198,12 +18198,12 @@
       </c>
       <c r="C364" s="2" t="inlineStr">
         <is>
-          <t>D14:12:2022</t>
+          <t>D14:2022:12</t>
         </is>
       </c>
       <c r="D364" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E364" s="2" t="inlineStr"/>
@@ -18246,12 +18246,12 @@
       </c>
       <c r="C365" s="2" t="inlineStr">
         <is>
-          <t>D15:13:2022</t>
+          <t>D15:2022:13</t>
         </is>
       </c>
       <c r="D365" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E365" s="2" t="inlineStr"/>
@@ -18294,12 +18294,12 @@
       </c>
       <c r="C366" s="2" t="inlineStr">
         <is>
-          <t>D15:14:2022</t>
+          <t>D15:2022:14</t>
         </is>
       </c>
       <c r="D366" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E366" s="2" t="inlineStr"/>
@@ -18342,12 +18342,12 @@
       </c>
       <c r="C367" s="2" t="inlineStr">
         <is>
-          <t>D15:15:2022</t>
+          <t>D15:2022:15</t>
         </is>
       </c>
       <c r="D367" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E367" s="2" t="inlineStr"/>
@@ -18390,12 +18390,12 @@
       </c>
       <c r="C368" s="2" t="inlineStr">
         <is>
-          <t>D16:16:2022</t>
+          <t>D16:2022:16</t>
         </is>
       </c>
       <c r="D368" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E368" s="2" t="inlineStr"/>
@@ -18438,12 +18438,12 @@
       </c>
       <c r="C369" s="2" t="inlineStr">
         <is>
-          <t>D16:17:2022</t>
+          <t>D16:2022:17</t>
         </is>
       </c>
       <c r="D369" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E369" s="2" t="inlineStr"/>
@@ -18486,12 +18486,12 @@
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>D16:18:2022</t>
+          <t>D16:2022:18</t>
         </is>
       </c>
       <c r="D370" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E370" s="2" t="inlineStr"/>
@@ -18534,12 +18534,12 @@
       </c>
       <c r="C371" s="2" t="inlineStr">
         <is>
-          <t>E1:19:2022</t>
+          <t>E1:2022:19</t>
         </is>
       </c>
       <c r="D371" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E371" s="2" t="inlineStr"/>
@@ -18582,12 +18582,12 @@
       </c>
       <c r="C372" s="2" t="inlineStr">
         <is>
-          <t>E1:20:2022</t>
+          <t>E1:2022:20</t>
         </is>
       </c>
       <c r="D372" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E372" s="2" t="inlineStr"/>
@@ -18630,12 +18630,12 @@
       </c>
       <c r="C373" s="2" t="inlineStr">
         <is>
-          <t>E1:21:2022</t>
+          <t>E1:2022:21</t>
         </is>
       </c>
       <c r="D373" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E373" s="2" t="inlineStr"/>
@@ -18678,12 +18678,12 @@
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>E2:22:2022</t>
+          <t>E2:2022:22</t>
         </is>
       </c>
       <c r="D374" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E374" s="2" t="inlineStr"/>
@@ -18726,12 +18726,12 @@
       </c>
       <c r="C375" s="2" t="inlineStr">
         <is>
-          <t>E2:23:2022</t>
+          <t>E2:2022:23</t>
         </is>
       </c>
       <c r="D375" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E375" s="2" t="inlineStr"/>
@@ -18774,12 +18774,12 @@
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>E2:24:2022</t>
+          <t>E2:2022:24</t>
         </is>
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E376" s="2" t="inlineStr"/>
@@ -18822,12 +18822,12 @@
       </c>
       <c r="C377" s="2" t="inlineStr">
         <is>
-          <t>E3:25:2022</t>
+          <t>E3:2022:25</t>
         </is>
       </c>
       <c r="D377" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E377" s="2" t="inlineStr"/>
@@ -18870,12 +18870,12 @@
       </c>
       <c r="C378" s="2" t="inlineStr">
         <is>
-          <t>E3:26:2022</t>
+          <t>E3:2022:26</t>
         </is>
       </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E378" s="2" t="inlineStr"/>
@@ -18918,12 +18918,12 @@
       </c>
       <c r="C379" s="2" t="inlineStr">
         <is>
-          <t>E3:27:2022</t>
+          <t>E3:2022:27</t>
         </is>
       </c>
       <c r="D379" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E379" s="2" t="inlineStr"/>
@@ -18966,12 +18966,12 @@
       </c>
       <c r="C380" s="2" t="inlineStr">
         <is>
-          <t>E4:28:2022</t>
+          <t>E4:2022:28</t>
         </is>
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E380" s="2" t="inlineStr"/>
@@ -19014,12 +19014,12 @@
       </c>
       <c r="C381" s="2" t="inlineStr">
         <is>
-          <t>E4:29:2022</t>
+          <t>E4:2022:29</t>
         </is>
       </c>
       <c r="D381" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E381" s="2" t="inlineStr"/>
@@ -19062,12 +19062,12 @@
       </c>
       <c r="C382" s="2" t="inlineStr">
         <is>
-          <t>E4:30:2022</t>
+          <t>E4:2022:30</t>
         </is>
       </c>
       <c r="D382" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E382" s="2" t="inlineStr"/>
@@ -19110,12 +19110,12 @@
       </c>
       <c r="C383" s="2" t="inlineStr">
         <is>
-          <t>E5:31:2022</t>
+          <t>E5:2022:31</t>
         </is>
       </c>
       <c r="D383" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E383" s="2" t="inlineStr"/>
@@ -19158,12 +19158,12 @@
       </c>
       <c r="C384" s="2" t="inlineStr">
         <is>
-          <t>E5:32:2022</t>
+          <t>E5:2022:32</t>
         </is>
       </c>
       <c r="D384" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E384" s="2" t="inlineStr"/>
@@ -19206,12 +19206,12 @@
       </c>
       <c r="C385" s="2" t="inlineStr">
         <is>
-          <t>E5:33:2022</t>
+          <t>E5:2022:33</t>
         </is>
       </c>
       <c r="D385" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E385" s="2" t="inlineStr"/>
@@ -19254,12 +19254,12 @@
       </c>
       <c r="C386" s="2" t="inlineStr">
         <is>
-          <t>E6:34:2022</t>
+          <t>E6:2022:34</t>
         </is>
       </c>
       <c r="D386" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E386" s="2" t="inlineStr"/>
@@ -19302,12 +19302,12 @@
       </c>
       <c r="C387" s="2" t="inlineStr">
         <is>
-          <t>E6:35:2022</t>
+          <t>E6:2022:35</t>
         </is>
       </c>
       <c r="D387" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E387" s="2" t="inlineStr"/>
@@ -19350,12 +19350,12 @@
       </c>
       <c r="C388" s="2" t="inlineStr">
         <is>
-          <t>E6:36:2022</t>
+          <t>E6:2022:36</t>
         </is>
       </c>
       <c r="D388" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E388" s="2" t="inlineStr"/>
@@ -19398,12 +19398,12 @@
       </c>
       <c r="C389" s="2" t="inlineStr">
         <is>
-          <t>D1:37:2022</t>
+          <t>D1:2022:37</t>
         </is>
       </c>
       <c r="D389" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E389" s="2" t="inlineStr"/>
@@ -19446,12 +19446,12 @@
       </c>
       <c r="C390" s="2" t="inlineStr">
         <is>
-          <t>D1:38:2022</t>
+          <t>D1:2022:38</t>
         </is>
       </c>
       <c r="D390" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E390" s="2" t="inlineStr"/>
@@ -19494,12 +19494,12 @@
       </c>
       <c r="C391" s="2" t="inlineStr">
         <is>
-          <t>D1:39:2022</t>
+          <t>D1:2022:39</t>
         </is>
       </c>
       <c r="D391" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E391" s="2" t="inlineStr"/>
@@ -19542,12 +19542,12 @@
       </c>
       <c r="C392" s="2" t="inlineStr">
         <is>
-          <t>D2:40:2022</t>
+          <t>D2:2022:40</t>
         </is>
       </c>
       <c r="D392" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E392" s="2" t="inlineStr"/>
@@ -19590,12 +19590,12 @@
       </c>
       <c r="C393" s="2" t="inlineStr">
         <is>
-          <t>D2:41:2022</t>
+          <t>D2:2022:41</t>
         </is>
       </c>
       <c r="D393" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E393" s="2" t="inlineStr"/>
@@ -19638,12 +19638,12 @@
       </c>
       <c r="C394" s="2" t="inlineStr">
         <is>
-          <t>D2:42:2022</t>
+          <t>D2:2022:42</t>
         </is>
       </c>
       <c r="D394" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E394" s="2" t="inlineStr"/>
@@ -19686,12 +19686,12 @@
       </c>
       <c r="C395" s="2" t="inlineStr">
         <is>
-          <t>D3:43:2022</t>
+          <t>D3:2022:43</t>
         </is>
       </c>
       <c r="D395" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E395" s="2" t="inlineStr"/>
@@ -19734,12 +19734,12 @@
       </c>
       <c r="C396" s="2" t="inlineStr">
         <is>
-          <t>D3:44:2022</t>
+          <t>D3:2022:44</t>
         </is>
       </c>
       <c r="D396" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E396" s="2" t="inlineStr"/>
@@ -19782,12 +19782,12 @@
       </c>
       <c r="C397" s="2" t="inlineStr">
         <is>
-          <t>D3:45:2022</t>
+          <t>D3:2022:45</t>
         </is>
       </c>
       <c r="D397" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E397" s="2" t="inlineStr"/>
@@ -19830,12 +19830,12 @@
       </c>
       <c r="C398" s="2" t="inlineStr">
         <is>
-          <t>D4:46:2022</t>
+          <t>D4:2022:46</t>
         </is>
       </c>
       <c r="D398" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E398" s="2" t="inlineStr"/>
@@ -19878,12 +19878,12 @@
       </c>
       <c r="C399" s="2" t="inlineStr">
         <is>
-          <t>D4:47:2022</t>
+          <t>D4:2022:47</t>
         </is>
       </c>
       <c r="D399" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E399" s="2" t="inlineStr"/>
@@ -19926,12 +19926,12 @@
       </c>
       <c r="C400" s="2" t="inlineStr">
         <is>
-          <t>D4:48:2022</t>
+          <t>D4:2022:48</t>
         </is>
       </c>
       <c r="D400" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E400" s="2" t="inlineStr"/>
@@ -19974,12 +19974,12 @@
       </c>
       <c r="C401" s="2" t="inlineStr">
         <is>
-          <t>D5:49:2022</t>
+          <t>D5:2022:49</t>
         </is>
       </c>
       <c r="D401" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E401" s="2" t="inlineStr"/>
@@ -20022,12 +20022,12 @@
       </c>
       <c r="C402" s="2" t="inlineStr">
         <is>
-          <t>D5:50:2022</t>
+          <t>D5:2022:50</t>
         </is>
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E402" s="2" t="inlineStr"/>
@@ -20070,12 +20070,12 @@
       </c>
       <c r="C403" s="2" t="inlineStr">
         <is>
-          <t>D5:51:2022</t>
+          <t>D5:2022:51</t>
         </is>
       </c>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E403" s="2" t="inlineStr"/>
@@ -20118,12 +20118,12 @@
       </c>
       <c r="C404" s="2" t="inlineStr">
         <is>
-          <t>D6:52:2022</t>
+          <t>D6:2022:52</t>
         </is>
       </c>
       <c r="D404" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E404" s="2" t="inlineStr"/>
@@ -20166,12 +20166,12 @@
       </c>
       <c r="C405" s="2" t="inlineStr">
         <is>
-          <t>D6:53:2022</t>
+          <t>D6:2022:53</t>
         </is>
       </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E405" s="2" t="inlineStr"/>
@@ -20214,12 +20214,12 @@
       </c>
       <c r="C406" s="2" t="inlineStr">
         <is>
-          <t>D6:54:2022</t>
+          <t>D6:2022:54</t>
         </is>
       </c>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E406" s="2" t="inlineStr"/>
@@ -20262,12 +20262,12 @@
       </c>
       <c r="C407" s="2" t="inlineStr">
         <is>
-          <t>E7:55:2022</t>
+          <t>E7:2022:55</t>
         </is>
       </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E407" s="2" t="inlineStr"/>
@@ -20310,12 +20310,12 @@
       </c>
       <c r="C408" s="2" t="inlineStr">
         <is>
-          <t>E7:56:2022</t>
+          <t>E7:2022:56</t>
         </is>
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E408" s="2" t="inlineStr"/>
@@ -20358,12 +20358,12 @@
       </c>
       <c r="C409" s="2" t="inlineStr">
         <is>
-          <t>E7:57:2022</t>
+          <t>E7:2022:57</t>
         </is>
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E409" s="2" t="inlineStr"/>
@@ -20406,12 +20406,12 @@
       </c>
       <c r="C410" s="2" t="inlineStr">
         <is>
-          <t>E8:58:2022</t>
+          <t>E8:2022:58</t>
         </is>
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E410" s="2" t="inlineStr"/>
@@ -20454,12 +20454,12 @@
       </c>
       <c r="C411" s="2" t="inlineStr">
         <is>
-          <t>E8:59:2022</t>
+          <t>E8:2022:59</t>
         </is>
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E411" s="2" t="inlineStr"/>
@@ -20502,12 +20502,12 @@
       </c>
       <c r="C412" s="2" t="inlineStr">
         <is>
-          <t>E8:60:2022</t>
+          <t>E8:2022:60</t>
         </is>
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E412" s="2" t="inlineStr"/>
@@ -20550,12 +20550,12 @@
       </c>
       <c r="C413" s="2" t="inlineStr">
         <is>
-          <t>E9:61:2022</t>
+          <t>E9:2022:61</t>
         </is>
       </c>
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E413" s="2" t="inlineStr"/>
@@ -20598,12 +20598,12 @@
       </c>
       <c r="C414" s="2" t="inlineStr">
         <is>
-          <t>E9:62:2022</t>
+          <t>E9:2022:62</t>
         </is>
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E414" s="2" t="inlineStr"/>
@@ -20646,12 +20646,12 @@
       </c>
       <c r="C415" s="2" t="inlineStr">
         <is>
-          <t>E9:63:2022</t>
+          <t>E9:2022:63</t>
         </is>
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E415" s="2" t="inlineStr"/>
@@ -20694,12 +20694,12 @@
       </c>
       <c r="C416" s="2" t="inlineStr">
         <is>
-          <t>E10:64:2022</t>
+          <t>E10:2022:64</t>
         </is>
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E416" s="2" t="inlineStr"/>
@@ -20742,12 +20742,12 @@
       </c>
       <c r="C417" s="2" t="inlineStr">
         <is>
-          <t>E10:65:2022</t>
+          <t>E10:2022:65</t>
         </is>
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E417" s="2" t="inlineStr"/>
@@ -20790,12 +20790,12 @@
       </c>
       <c r="C418" s="2" t="inlineStr">
         <is>
-          <t>E10:66:2022</t>
+          <t>E10:2022:66</t>
         </is>
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E418" s="2" t="inlineStr"/>
@@ -20838,12 +20838,12 @@
       </c>
       <c r="C419" s="2" t="inlineStr">
         <is>
-          <t>E11:67:2022</t>
+          <t>E11:2022:67</t>
         </is>
       </c>
       <c r="D419" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E419" s="2" t="inlineStr"/>
@@ -20886,12 +20886,12 @@
       </c>
       <c r="C420" s="2" t="inlineStr">
         <is>
-          <t>E11:68:2022</t>
+          <t>E11:2022:68</t>
         </is>
       </c>
       <c r="D420" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E420" s="2" t="inlineStr"/>
@@ -20934,12 +20934,12 @@
       </c>
       <c r="C421" s="2" t="inlineStr">
         <is>
-          <t>E11:69:2022</t>
+          <t>E11:2022:69</t>
         </is>
       </c>
       <c r="D421" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E421" s="2" t="inlineStr"/>
@@ -20982,12 +20982,12 @@
       </c>
       <c r="C422" s="2" t="inlineStr">
         <is>
-          <t>E12:70:2022</t>
+          <t>E12:2022:70</t>
         </is>
       </c>
       <c r="D422" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E422" s="2" t="inlineStr"/>
@@ -21030,12 +21030,12 @@
       </c>
       <c r="C423" s="2" t="inlineStr">
         <is>
-          <t>E12:71:2022</t>
+          <t>E12:2022:71</t>
         </is>
       </c>
       <c r="D423" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E423" s="2" t="inlineStr"/>
@@ -21078,12 +21078,12 @@
       </c>
       <c r="C424" s="2" t="inlineStr">
         <is>
-          <t>E12:72:2022</t>
+          <t>E12:2022:72</t>
         </is>
       </c>
       <c r="D424" s="2" t="inlineStr">
         <is>
-          <t>Plot:ID:date</t>
+          <t>Plot:date:ID</t>
         </is>
       </c>
       <c r="E424" s="2" t="inlineStr"/>
